--- a/data/TransportOpt.xlsx
+++ b/data/TransportOpt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://techsource-my.sharepoint.com/personal/phudit_sombutsirinun_ascendas-asia_com/Documents/Ascendas/Support/BU/BA Workshop/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{9001BED7-13B6-43A6-BF26-2FB3E068E14B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{565AF651-7CDC-48C6-B0E1-4B261FDD5500}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{9001BED7-13B6-43A6-BF26-2FB3E068E14B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5450D362-13C3-4677-A914-2566B93334AA}"/>
   <bookViews>
-    <workbookView xWindow="-21105" yWindow="2325" windowWidth="17250" windowHeight="8865" activeTab="2" xr2:uid="{5FAC0EEE-BE06-45AA-A28E-E672D3B9C284}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{5FAC0EEE-BE06-45AA-A28E-E672D3B9C284}"/>
   </bookViews>
   <sheets>
     <sheet name="Shipping Cost" sheetId="1" r:id="rId1"/>
@@ -139,15 +139,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -509,24 +506,24 @@
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="1">
@@ -546,7 +543,7 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1">
@@ -566,7 +563,7 @@
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="1">
@@ -606,12 +603,12 @@
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="1">
@@ -619,7 +616,7 @@
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1">
@@ -627,7 +624,7 @@
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="1">
@@ -649,31 +646,31 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="1">
+        <v>0.217</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1">
         <v>0.26500000000000001</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0.217</v>
-      </c>
-    </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="1">
@@ -681,7 +678,7 @@
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="1">
@@ -689,7 +686,7 @@
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
